--- a/Result/profitability/1446.xlsx
+++ b/Result/profitability/1446.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.23</v>
       </c>
       <c r="M2" t="n">
-        <v>0.99875</v>
+        <v>0.42375</v>
       </c>
       <c r="N2" t="n">
-        <v>37.96125</v>
+        <v>36.965</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.13</v>
       </c>
       <c r="M3" t="n">
-        <v>0.37375</v>
+        <v>0.31125</v>
       </c>
       <c r="N3" t="n">
-        <v>33.73</v>
+        <v>33.09625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.28125</v>
+        <v>0.2625</v>
       </c>
       <c r="N4" t="n">
-        <v>31.09625</v>
+        <v>30.72125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0.22375</v>
+        <v>0.12875</v>
       </c>
       <c r="N5" t="n">
-        <v>29.4525</v>
+        <v>28.6625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>0.10625</v>
+        <v>0.06625</v>
       </c>
       <c r="N6" t="n">
-        <v>26.74625</v>
+        <v>26.705</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0475</v>
+        <v>0.13375</v>
       </c>
       <c r="N7" t="n">
-        <v>25.00375</v>
+        <v>30.30125</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.10875</v>
+        <v>0.07999999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>28.11625</v>
+        <v>28.58375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03750000000000001</v>
+        <v>0.0375</v>
       </c>
       <c r="N9" t="n">
         <v>26.7175</v>
@@ -1645,7 +1645,7 @@
         <v>0.11</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02250000000000001</v>
+        <v>0.0225</v>
       </c>
       <c r="N10" t="n">
         <v>26.66125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1446</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>152</v>
+      </c>
+      <c r="D75" t="n">
+        <v>87</v>
+      </c>
+      <c r="E75" t="n">
+        <v>65</v>
+      </c>
+      <c r="F75" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="G75" t="n">
+        <v>30</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>20.03%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>40</v>
+      </c>
+      <c r="K75" t="n">
+        <v>37</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.00375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.91125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.740000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09565217391304359</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7378640776699029</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-6.319999999999993</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1285598047192839</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
